--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,450 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128039855</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80123</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Västra stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>518013</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6944210</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128039856</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98477</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västra stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6944185</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128039852</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56846</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>517916</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6944141</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128039854</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80027</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518049</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6944203</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128039855</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128039852</v>
       </c>
       <c r="B5" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128039854</v>
       </c>
       <c r="B6" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128039855</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128039852</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128039854</v>
       </c>
       <c r="B6" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128039855</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98491</v>
+        <v>98499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128039854</v>
       </c>
       <c r="B6" t="n">
-        <v>80036</v>
+        <v>80039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128039855</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98499</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128039852</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128039854</v>
       </c>
       <c r="B6" t="n">
-        <v>80039</v>
+        <v>80092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128039855</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128039856</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128039852</v>
       </c>
       <c r="B5" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>128039854</v>
       </c>
       <c r="B6" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80557224</v>
+        <v>1976545</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Sverige, Jmt</t>
+          <t>Rången, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518035.8452918676</v>
+        <v>517973</v>
       </c>
       <c r="R2" t="n">
-        <v>6944209.198034458</v>
+        <v>6944277</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,48 +756,57 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
+          <t>Sara Toivanen Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Noro-Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sara Toivanen Jonsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128039855</v>
+        <v>128039854</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518013</v>
+        <v>518049</v>
       </c>
       <c r="R3" t="n">
-        <v>6944210</v>
+        <v>6944203</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128039856</v>
+        <v>128039855</v>
       </c>
       <c r="B4" t="n">
-        <v>98606</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517865</v>
+        <v>518013</v>
       </c>
       <c r="R4" t="n">
-        <v>6944185</v>
+        <v>6944210</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,52 +1003,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128039852</v>
+        <v>80557224</v>
       </c>
       <c r="B5" t="n">
-        <v>56871</v>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra stugusjön, Jmt</t>
+          <t>Norra Sverige, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517916</v>
+        <v>518036</v>
       </c>
       <c r="R5" t="n">
-        <v>6944141</v>
+        <v>6944209</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,22 +1068,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2019-07-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128039854</v>
+        <v>128039852</v>
       </c>
       <c r="B6" t="n">
-        <v>80096</v>
+        <v>57132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,26 +1121,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518049</v>
+        <v>517916</v>
       </c>
       <c r="R6" t="n">
-        <v>6944203</v>
+        <v>6944141</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,6 +1218,117 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128039856</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västra stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>517865</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6944185</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53280-2022 artfynd.xlsx
+++ b/artfynd/A 53280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976545</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128039854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128039855</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80557224</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128039852</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,8 +1359,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128039856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>